--- a/docs/Z曲げ_実績記入シート.xlsx
+++ b/docs/Z曲げ_実績記入シート.xlsx
@@ -239,7 +239,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -409,6 +409,9 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -663,7 +666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:U74"/>
+  <dimension ref="A1:X84"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="7" customWidth="1" style="27" min="1" max="1"/>
@@ -753,6 +756,11 @@
           <t>シミュレーション（2026-09-11 実行）</t>
         </is>
       </c>
+      <c r="V6" s="35" t="inlineStr">
+        <is>
+          <t>フランジA上限の突き合わせ（2026-09-11）</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="31.5" customHeight="1" s="28">
       <c r="A7" s="36" t="inlineStr">
@@ -795,9 +803,10 @@
           <t>段差S 幾何</t>
         </is>
       </c>
-      <c r="I7" s="39" t="inlineStr">
-        <is>
-          <t>フランジA 最小</t>
+      <c r="I7" s="58" t="inlineStr">
+        <is>
+          <t>フランジA 上限
+（その段差Sのとき）</t>
         </is>
       </c>
       <c r="J7" s="39" t="inlineStr">
@@ -858,6 +867,21 @@
       <c r="U7" s="42" t="inlineStr">
         <is>
           <t>計算条件</t>
+        </is>
+      </c>
+      <c r="V7" s="42" t="inlineStr">
+        <is>
+          <t>sim フランジA上限</t>
+        </is>
+      </c>
+      <c r="W7" s="42" t="inlineStr">
+        <is>
+          <t>実績−sim</t>
+        </is>
+      </c>
+      <c r="X7" s="42" t="inlineStr">
+        <is>
+          <t>判定</t>
         </is>
       </c>
     </row>
@@ -952,6 +976,17 @@
           <t>ヤゲン904061／両端フランジ80mm／971561 V8ｲﾝｻｰﾄ＋スタック（bending.dxf の一般化・参考）</t>
         </is>
       </c>
+      <c r="V9" s="51" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="W9" s="51" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="X9" s="51" t="inlineStr">
+        <is>
+          <t>ほぼ一致</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="29.85" customHeight="1" s="28">
       <c r="A10" s="44" t="inlineStr">
@@ -1021,6 +1056,17 @@
           <t>ヤゲン904061／両端フランジ80mm／971561 V8ｲﾝｻｰﾄ＋スタック（bending.dxf の一般化・参考）</t>
         </is>
       </c>
+      <c r="V10" s="51" t="n">
+        <v>45.8</v>
+      </c>
+      <c r="W10" s="51" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="X10" s="51" t="inlineStr">
+        <is>
+          <t>ほぼ一致</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="28">
       <c r="A11" s="44" t="inlineStr">
@@ -1088,6 +1134,17 @@
           <t>ヤゲン904061／両端フランジ80mm／974061 V12ｲﾝｻｰﾄ＋台（図面実測）</t>
         </is>
       </c>
+      <c r="V11" s="51" t="n">
+        <v>97.09999999999999</v>
+      </c>
+      <c r="W11" s="51" t="n">
+        <v>-48.1</v>
+      </c>
+      <c r="X11" s="51" t="inlineStr">
+        <is>
+          <t>シミュレーションが甘い（危険）</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="15" customHeight="1" s="28">
       <c r="A12" s="44" t="inlineStr">
@@ -1155,6 +1212,17 @@
           <t>ヤゲン904061／両端フランジ80mm／974061 V12ｲﾝｻｰﾄ＋台（図面実測）</t>
         </is>
       </c>
+      <c r="V12" s="51" t="n">
+        <v>97.2</v>
+      </c>
+      <c r="W12" s="51" t="n">
+        <v>-47.7</v>
+      </c>
+      <c r="X12" s="51" t="inlineStr">
+        <is>
+          <t>シミュレーションが甘い（危険）</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="29.85" customHeight="1" s="28">
       <c r="A13" s="44" t="inlineStr">
@@ -1226,6 +1294,17 @@
           <t>ヤゲン904061／両端フランジ80mm／974061 V12ｲﾝｻｰﾄ＋台（図面実測）</t>
         </is>
       </c>
+      <c r="V13" s="51" t="n">
+        <v>97.7</v>
+      </c>
+      <c r="W13" s="51" t="n">
+        <v>-47.7</v>
+      </c>
+      <c r="X13" s="51" t="inlineStr">
+        <is>
+          <t>シミュレーションが甘い（危険）</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="15" customHeight="1" s="28">
       <c r="A14" s="44" t="inlineStr">
@@ -1291,6 +1370,17 @@
           <t>ヤゲン904061／両端フランジ80mm／977061 V16ｲﾝｻｰﾄ＋スタック（bending.dxf の一般化・参考）</t>
         </is>
       </c>
+      <c r="V14" s="51" t="n">
+        <v>91.09999999999999</v>
+      </c>
+      <c r="W14" s="51" t="n">
+        <v>-41.1</v>
+      </c>
+      <c r="X14" s="51" t="inlineStr">
+        <is>
+          <t>シミュレーションが甘い（危険）</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="29.85" customHeight="1" s="28">
       <c r="A15" s="44" t="inlineStr">
@@ -1360,6 +1450,17 @@
           <t>ヤゲン904061／両端フランジ80mm／977061 V16ｲﾝｻｰﾄ＋スタック（bending.dxf の一般化・参考）</t>
         </is>
       </c>
+      <c r="V15" s="51" t="n">
+        <v>91.5</v>
+      </c>
+      <c r="W15" s="51" t="n">
+        <v>-40.5</v>
+      </c>
+      <c r="X15" s="51" t="inlineStr">
+        <is>
+          <t>シミュレーションが甘い（危険）</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="15" customHeight="1" s="28">
       <c r="A16" s="44" t="inlineStr">
@@ -1425,6 +1526,17 @@
           <t>ヤゲン904061／両端フランジ80mm／979061 V20ｲﾝｻｰﾄ＋スタック（bending.dxf の一般化・参考）</t>
         </is>
       </c>
+      <c r="V16" s="51" t="n">
+        <v>91.5</v>
+      </c>
+      <c r="W16" s="51" t="n">
+        <v>-40.5</v>
+      </c>
+      <c r="X16" s="51" t="inlineStr">
+        <is>
+          <t>シミュレーションが甘い（危険）</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="15" customHeight="1" s="28">
       <c r="A17" s="44" t="inlineStr">
@@ -1488,6 +1600,17 @@
       <c r="U17" s="51" t="inlineStr">
         <is>
           <t>ヤゲン904061／両端フランジ80mm／979061 V20ｲﾝｻｰﾄ＋スタック（bending.dxf の一般化・参考）</t>
+        </is>
+      </c>
+      <c r="V17" s="51" t="n">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="W17" s="51" t="n">
+        <v>-40.1</v>
+      </c>
+      <c r="X17" s="51" t="inlineStr">
+        <is>
+          <t>シミュレーションが甘い（危険）</t>
         </is>
       </c>
     </row>
@@ -1557,6 +1680,17 @@
           <t>ヤゲン904061／両端フランジ80mm／982061 V25ｲﾝｻｰﾄ＋台（図面実測）</t>
         </is>
       </c>
+      <c r="V18" s="51" t="n">
+        <v>98</v>
+      </c>
+      <c r="W18" s="51" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X18" s="51" t="inlineStr">
+        <is>
+          <t>ほぼ一致</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="15" customHeight="1" s="28">
       <c r="A19" s="44" t="inlineStr">
@@ -1620,6 +1754,17 @@
           <t>ヤゲン904061／両端フランジ80mm／982061 V25ｲﾝｻｰﾄ＋台（図面実測）</t>
         </is>
       </c>
+      <c r="V19" s="51" t="n">
+        <v>98.7</v>
+      </c>
+      <c r="W19" s="51" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="X19" s="51" t="inlineStr">
+        <is>
+          <t>ほぼ一致</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="15" customHeight="1" s="28">
       <c r="A20" s="44" t="inlineStr">
@@ -1681,6 +1826,17 @@
           <t>ヤゲン904061／両端フランジ80mm／982061 V25ｲﾝｻｰﾄ＋台（図面実測）</t>
         </is>
       </c>
+      <c r="V20" s="51" t="n">
+        <v>99</v>
+      </c>
+      <c r="W20" s="51" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="X20" s="51" t="inlineStr">
+        <is>
+          <t>ほぼ一致</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="29.85" customHeight="1" s="28">
       <c r="A21" s="44" t="inlineStr">
@@ -1748,6 +1904,17 @@
           <t>ヤゲン904061／両端フランジ80mm／982061 V25ｲﾝｻｰﾄ＋台（図面実測）</t>
         </is>
       </c>
+      <c r="V21" s="51" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="W21" s="51" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="X21" s="51" t="inlineStr">
+        <is>
+          <t>ほぼ一致</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="29.85" customHeight="1" s="28">
       <c r="A22" s="44" t="inlineStr">
@@ -1815,6 +1982,17 @@
           <t>ヤゲン904061／両端フランジ80mm／03500 V32</t>
         </is>
       </c>
+      <c r="V22" s="51" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="W22" s="51" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="X22" s="51" t="inlineStr">
+        <is>
+          <t>ほぼ一致</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="15" customHeight="1" s="28">
       <c r="A23" s="44" t="inlineStr">
@@ -1878,6 +2056,17 @@
           <t>ヤゲン904061／両端フランジ80mm／03500 V32</t>
         </is>
       </c>
+      <c r="V23" s="51" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="W23" s="51" t="n">
+        <v>-4.1</v>
+      </c>
+      <c r="X23" s="51" t="inlineStr">
+        <is>
+          <t>ほぼ一致</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="15" customHeight="1" s="28">
       <c r="A24" s="44" t="inlineStr">
@@ -1939,6 +2128,17 @@
           <t>ヤゲン904061／両端フランジ80mm／03500 V32</t>
         </is>
       </c>
+      <c r="V24" s="51" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="W24" s="51" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="X24" s="51" t="inlineStr">
+        <is>
+          <t>ほぼ一致</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="15" customHeight="1" s="28">
       <c r="A25" s="44" t="inlineStr">
@@ -2004,6 +2204,17 @@
       <c r="U25" s="51" t="inlineStr">
         <is>
           <t>ヤゲン904061／両端フランジ80mm／03500 V32</t>
+        </is>
+      </c>
+      <c r="V25" s="51" t="n">
+        <v>103</v>
+      </c>
+      <c r="W25" s="51" t="n">
+        <v>-3</v>
+      </c>
+      <c r="X25" s="51" t="inlineStr">
+        <is>
+          <t>ほぼ一致</t>
         </is>
       </c>
     </row>
@@ -3673,51 +3884,114 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
+      <c r="A68" s="27" t="inlineStr">
         <is>
           <t>※ シミュレーション列（R〜U）は bending-simulator.jsx の干渉判定そのものを使って、</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
+      <c r="A69" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">　 その段差をどこまで小さくできるかを二分探索した結果です（scripts/z-sim.mjs）。</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
+      <c r="A70" s="27" t="inlineStr">
         <is>
           <t>※ 条件：上型はヤゲン904061、両端フランジは80mm（折り曲げ表の最小外寸が大きい型はその値＋15mm）。</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
+      <c r="A71" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">　 曲げ順は 1曲げ目→2曲げ目（2工程目は裏返し）。金型は各V幅の代表1本、実測台があるものは台込み。</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
+      <c r="A72" s="27" t="inlineStr">
         <is>
           <t>※「厳しいほう」＝実績とシミュレーションの大きいほう。実務ではこちらを下回らないようにしてください。</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
+      <c r="A73" s="27" t="inlineStr">
         <is>
           <t>※「実績−sim」がプラスなら実績のほうが大きい（幾何の計算が甘い）、マイナスならシミュレーションのほうが厳しい。</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
+      <c r="A74" s="27" t="inlineStr">
         <is>
           <t>※ V100以上が算出できずなのは、折り曲げ表の最小外寸が大きくフランジが長くなるため、段差を広げても通らないためです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>※【重要な訂正】I列は「フランジA 最小」という見出しでしたが、実際には</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　 その行の段差Sのときに取れる フランジAの“最大” です（超えるとVの台に当たる）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　 例：V8・PL1.2・S=15.5 のとき A は 49 まで。50 にすると曲がりません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　 備考欄の「S35の場合 A95」は、段差を35にすればAを95まで伸ばせるという意味です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>※ V〜X列は、同じ段差Sでシミュレーションが出したフランジAの上限です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　 条件：上型ヤゲン904061、反対側のフランジBは30mm固定（A側だけを見るため）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>※ 突き合わせの結果：V25・V32 は実績とほぼ一致（差0.5〜4.5mm）。V8 はシミュレーションが</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　 3.4〜3.7mm 厳しめ。いっぽう V12・V16・V20 はシミュレーションが 40〜48mm も甘く出ます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　 実績では50mm前後で台に当たるのに、モデルには その高さの障害物がありません。要調査。</t>
         </is>
       </c>
     </row>

--- a/docs/Z曲げ_実績記入シート.xlsx
+++ b/docs/Z曲げ_実績記入シート.xlsx
@@ -9,7 +9,10 @@
   <sheets>
     <sheet name="Z曲げ実績" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Z曲げ実績'!$6:$7</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Z曲げ実績'!$A$1:$X$84</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
 </file>
@@ -239,7 +242,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -412,6 +415,29 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -664,25 +690,35 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:X84"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="7" customWidth="1" style="27" min="1" max="1"/>
-    <col width="6" customWidth="1" style="27" min="2" max="2"/>
-    <col width="8" customWidth="1" style="27" min="3" max="3"/>
-    <col width="6" customWidth="1" style="27" min="4" max="4"/>
-    <col width="7" customWidth="1" style="27" min="5" max="5"/>
-    <col width="13" customWidth="1" style="27" min="6" max="6"/>
-    <col width="10" customWidth="1" style="27" min="7" max="8"/>
-    <col width="11" customWidth="1" style="27" min="9" max="10"/>
-    <col width="10" customWidth="1" style="27" min="11" max="11"/>
-    <col width="11" customWidth="1" style="27" min="12" max="13"/>
-    <col width="20" customWidth="1" style="27" min="14" max="14"/>
-    <col width="11" customWidth="1" style="27" min="15" max="15"/>
-    <col width="12" customWidth="1" style="27" min="16" max="16"/>
-    <col width="42" customWidth="1" style="27" min="17" max="17"/>
+    <col width="6" customWidth="1" style="27" min="1" max="1"/>
+    <col width="5" customWidth="1" style="27" min="2" max="2"/>
+    <col width="6.5" customWidth="1" style="27" min="3" max="3"/>
+    <col width="5" customWidth="1" style="27" min="4" max="4"/>
+    <col width="6" customWidth="1" style="27" min="5" max="5"/>
+    <col width="9" customWidth="1" style="27" min="6" max="6"/>
+    <col width="8" customWidth="1" style="27" min="7" max="8"/>
+    <col width="8" customWidth="1" style="28" min="8" max="8"/>
+    <col width="10" customWidth="1" style="27" min="9" max="10"/>
+    <col width="8" customWidth="1" style="28" min="10" max="10"/>
+    <col width="8" customWidth="1" style="27" min="11" max="11"/>
+    <col width="8" customWidth="1" style="27" min="12" max="13"/>
+    <col width="8" customWidth="1" style="28" min="13" max="13"/>
+    <col width="15" customWidth="1" style="27" min="14" max="14"/>
+    <col width="8" customWidth="1" style="27" min="15" max="15"/>
+    <col width="8" customWidth="1" style="27" min="16" max="16"/>
+    <col width="28" customWidth="1" style="27" min="17" max="17"/>
+    <col width="8.5" customWidth="1" style="28" min="18" max="18"/>
+    <col width="8" customWidth="1" style="28" min="19" max="19"/>
+    <col width="8" customWidth="1" style="28" min="20" max="20"/>
+    <col width="24" customWidth="1" style="28" min="21" max="21"/>
+    <col width="9" customWidth="1" style="28" min="22" max="22"/>
+    <col width="8" customWidth="1" style="28" min="23" max="23"/>
+    <col width="14" customWidth="1" style="28" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1" ht="21.6" customHeight="1" s="28">
@@ -903,10 +939,11 @@
       <c r="K8" s="33" t="n"/>
       <c r="L8" s="33" t="n"/>
       <c r="M8" s="33" t="n"/>
-      <c r="N8" s="33" t="n"/>
+      <c r="N8" s="59" t="n"/>
       <c r="O8" s="33" t="n"/>
       <c r="P8" s="33" t="n"/>
-      <c r="Q8" s="33" t="n"/>
+      <c r="Q8" s="59" t="n"/>
+      <c r="U8" s="60" t="n"/>
     </row>
     <row r="9" ht="29.85" customHeight="1" s="28">
       <c r="A9" s="44" t="inlineStr">
@@ -944,7 +981,7 @@
       </c>
       <c r="L9" s="47" t="n"/>
       <c r="M9" s="47" t="n"/>
-      <c r="N9" s="48" t="inlineStr">
+      <c r="N9" s="61" t="inlineStr">
         <is>
           <t>S35の場合 A95</t>
         </is>
@@ -957,7 +994,7 @@
         <f>IF(OR(K9="",O9=""),"",K9-O9)</f>
         <v/>
       </c>
-      <c r="Q9" s="50" t="inlineStr">
+      <c r="Q9" s="62" t="inlineStr">
         <is>
           <t>フランジA最小・段差S最小とも修正液の上に書き直し。49 と読んだが要確認</t>
         </is>
@@ -971,7 +1008,7 @@
       <c r="T9" s="51" t="n">
         <v>-4.2</v>
       </c>
-      <c r="U9" s="51" t="inlineStr">
+      <c r="U9" s="63" t="inlineStr">
         <is>
           <t>ヤゲン904061／両端フランジ80mm／971561 V8ｲﾝｻｰﾄ＋スタック（bending.dxf の一般化・参考）</t>
         </is>
@@ -1024,7 +1061,7 @@
       </c>
       <c r="L10" s="47" t="n"/>
       <c r="M10" s="47" t="n"/>
-      <c r="N10" s="52" t="inlineStr">
+      <c r="N10" s="64" t="inlineStr">
         <is>
           <t>〃 A95.5</t>
         </is>
@@ -1037,7 +1074,7 @@
         <f>IF(OR(K10="",O10=""),"",K10-O10)</f>
         <v/>
       </c>
-      <c r="Q10" s="50" t="inlineStr">
+      <c r="Q10" s="62" t="inlineStr">
         <is>
           <t>フランジA最小は修正液の上。49.5 と読んだが要確認</t>
         </is>
@@ -1051,7 +1088,7 @@
       <c r="T10" s="51" t="n">
         <v>-4.5</v>
       </c>
-      <c r="U10" s="51" t="inlineStr">
+      <c r="U10" s="63" t="inlineStr">
         <is>
           <t>ヤゲン904061／両端フランジ80mm／971561 V8ｲﾝｻｰﾄ＋スタック（bending.dxf の一般化・参考）</t>
         </is>
@@ -1106,7 +1143,7 @@
       </c>
       <c r="L11" s="47" t="n"/>
       <c r="M11" s="47" t="n"/>
-      <c r="N11" s="48" t="inlineStr">
+      <c r="N11" s="61" t="inlineStr">
         <is>
           <t>S37の場合 A95</t>
         </is>
@@ -1119,7 +1156,7 @@
         <f>IF(OR(K11="",O11=""),"",K11-O11)</f>
         <v/>
       </c>
-      <c r="Q11" s="50" t="n"/>
+      <c r="Q11" s="62" t="n"/>
       <c r="R11" s="51" t="n">
         <v>21</v>
       </c>
@@ -1129,7 +1166,7 @@
       <c r="T11" s="51" t="n">
         <v>1.5</v>
       </c>
-      <c r="U11" s="51" t="inlineStr">
+      <c r="U11" s="63" t="inlineStr">
         <is>
           <t>ヤゲン904061／両端フランジ80mm／974061 V12ｲﾝｻｰﾄ＋台（図面実測）</t>
         </is>
@@ -1184,7 +1221,7 @@
       </c>
       <c r="L12" s="47" t="n"/>
       <c r="M12" s="47" t="n"/>
-      <c r="N12" s="52" t="inlineStr">
+      <c r="N12" s="64" t="inlineStr">
         <is>
           <t>〃 A95.5</t>
         </is>
@@ -1197,7 +1234,7 @@
         <f>IF(OR(K12="",O12=""),"",K12-O12)</f>
         <v/>
       </c>
-      <c r="Q12" s="50" t="n"/>
+      <c r="Q12" s="62" t="n"/>
       <c r="R12" s="51" t="n">
         <v>21.6</v>
       </c>
@@ -1207,7 +1244,7 @@
       <c r="T12" s="51" t="n">
         <v>1.4</v>
       </c>
-      <c r="U12" s="51" t="inlineStr">
+      <c r="U12" s="63" t="inlineStr">
         <is>
           <t>ヤゲン904061／両端フランジ80mm／974061 V12ｲﾝｻｰﾄ＋台（図面実測）</t>
         </is>
@@ -1262,7 +1299,7 @@
       </c>
       <c r="L13" s="47" t="n"/>
       <c r="M13" s="47" t="n"/>
-      <c r="N13" s="48" t="inlineStr">
+      <c r="N13" s="61" t="inlineStr">
         <is>
           <t>S38の場合 A96</t>
         </is>
@@ -1275,7 +1312,7 @@
         <f>IF(OR(K13="",O13=""),"",K13-O13)</f>
         <v/>
       </c>
-      <c r="Q13" s="50" t="inlineStr">
+      <c r="Q13" s="62" t="inlineStr">
         <is>
           <t>段差S最小は印刷の 12.3 を修正液で消して 24 と書き直し</t>
         </is>
@@ -1289,7 +1326,7 @@
       <c r="T13" s="51" t="n">
         <v>1.1</v>
       </c>
-      <c r="U13" s="51" t="inlineStr">
+      <c r="U13" s="63" t="inlineStr">
         <is>
           <t>ヤゲン904061／両端フランジ80mm／974061 V12ｲﾝｻｰﾄ＋台（図面実測）</t>
         </is>
@@ -1342,7 +1379,7 @@
       </c>
       <c r="L14" s="47" t="n"/>
       <c r="M14" s="47" t="n"/>
-      <c r="N14" s="48" t="inlineStr">
+      <c r="N14" s="61" t="inlineStr">
         <is>
           <t>S40の場合 A96</t>
         </is>
@@ -1355,7 +1392,7 @@
         <f>IF(OR(K14="",O14=""),"",K14-O14)</f>
         <v/>
       </c>
-      <c r="Q14" s="50" t="n"/>
+      <c r="Q14" s="62" t="n"/>
       <c r="R14" s="51" t="n">
         <v>22.1</v>
       </c>
@@ -1365,7 +1402,7 @@
       <c r="T14" s="51" t="n">
         <v>7.9</v>
       </c>
-      <c r="U14" s="51" t="inlineStr">
+      <c r="U14" s="63" t="inlineStr">
         <is>
           <t>ヤゲン904061／両端フランジ80mm／977061 V16ｲﾝｻｰﾄ＋スタック（bending.dxf の一般化・参考）</t>
         </is>
@@ -1418,7 +1455,7 @@
       </c>
       <c r="L15" s="47" t="n"/>
       <c r="M15" s="47" t="n"/>
-      <c r="N15" s="48" t="inlineStr">
+      <c r="N15" s="61" t="inlineStr">
         <is>
           <t>S42の場合 A97</t>
         </is>
@@ -1431,7 +1468,7 @@
         <f>IF(OR(K15="",O15=""),"",K15-O15)</f>
         <v/>
       </c>
-      <c r="Q15" s="50" t="inlineStr">
+      <c r="Q15" s="62" t="inlineStr">
         <is>
           <t>フランジB最小の欄に「ℓ200」と記入あり（長さ200の意味か要確認）</t>
         </is>
@@ -1445,7 +1482,7 @@
       <c r="T15" s="51" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="U15" s="51" t="inlineStr">
+      <c r="U15" s="63" t="inlineStr">
         <is>
           <t>ヤゲン904061／両端フランジ80mm／977061 V16ｲﾝｻｰﾄ＋スタック（bending.dxf の一般化・参考）</t>
         </is>
@@ -1498,7 +1535,7 @@
       </c>
       <c r="L16" s="47" t="n"/>
       <c r="M16" s="47" t="n"/>
-      <c r="N16" s="48" t="inlineStr">
+      <c r="N16" s="61" t="inlineStr">
         <is>
           <t>S43の場合 A97</t>
         </is>
@@ -1511,7 +1548,7 @@
         <f>IF(OR(K16="",O16=""),"",K16-O16)</f>
         <v/>
       </c>
-      <c r="Q16" s="50" t="n"/>
+      <c r="Q16" s="62" t="n"/>
       <c r="R16" s="51" t="n">
         <v>23.9</v>
       </c>
@@ -1521,7 +1558,7 @@
       <c r="T16" s="51" t="n">
         <v>14.1</v>
       </c>
-      <c r="U16" s="51" t="inlineStr">
+      <c r="U16" s="63" t="inlineStr">
         <is>
           <t>ヤゲン904061／両端フランジ80mm／979061 V20ｲﾝｻｰﾄ＋スタック（bending.dxf の一般化・参考）</t>
         </is>
@@ -1574,7 +1611,7 @@
       </c>
       <c r="L17" s="47" t="n"/>
       <c r="M17" s="47" t="n"/>
-      <c r="N17" s="48" t="inlineStr">
+      <c r="N17" s="61" t="inlineStr">
         <is>
           <t>S45の場合 A98</t>
         </is>
@@ -1587,7 +1624,7 @@
         <f>IF(OR(K17="",O17=""),"",K17-O17)</f>
         <v/>
       </c>
-      <c r="Q17" s="50" t="n"/>
+      <c r="Q17" s="62" t="n"/>
       <c r="R17" s="51" t="n">
         <v>26.1</v>
       </c>
@@ -1597,7 +1634,7 @@
       <c r="T17" s="51" t="n">
         <v>13.9</v>
       </c>
-      <c r="U17" s="51" t="inlineStr">
+      <c r="U17" s="63" t="inlineStr">
         <is>
           <t>ヤゲン904061／両端フランジ80mm／979061 V20ｲﾝｻｰﾄ＋スタック（bending.dxf の一般化・参考）</t>
         </is>
@@ -1652,7 +1689,7 @@
       </c>
       <c r="L18" s="47" t="n"/>
       <c r="M18" s="47" t="n"/>
-      <c r="N18" s="48" t="n"/>
+      <c r="N18" s="61" t="n"/>
       <c r="O18" s="49">
         <f>IF(AND(G18="",H18=""),"",MAX(G18,H18))</f>
         <v/>
@@ -1661,7 +1698,7 @@
         <f>IF(OR(K18="",O18=""),"",K18-O18)</f>
         <v/>
       </c>
-      <c r="Q18" s="50" t="inlineStr">
+      <c r="Q18" s="62" t="inlineStr">
         <is>
           <t>フランジA最小は修正液の上。97 と読んだ</t>
         </is>
@@ -1675,7 +1712,7 @@
       <c r="T18" s="51" t="n">
         <v>19</v>
       </c>
-      <c r="U18" s="51" t="inlineStr">
+      <c r="U18" s="63" t="inlineStr">
         <is>
           <t>ヤゲン904061／両端フランジ80mm／982061 V25ｲﾝｻｰﾄ＋台（図面実測）</t>
         </is>
@@ -1730,7 +1767,7 @@
       </c>
       <c r="L19" s="47" t="n"/>
       <c r="M19" s="47" t="n"/>
-      <c r="N19" s="48" t="n"/>
+      <c r="N19" s="61" t="n"/>
       <c r="O19" s="49">
         <f>IF(AND(G19="",H19=""),"",MAX(G19,H19))</f>
         <v/>
@@ -1739,7 +1776,7 @@
         <f>IF(OR(K19="",O19=""),"",K19-O19)</f>
         <v/>
       </c>
-      <c r="Q19" s="50" t="n"/>
+      <c r="Q19" s="62" t="n"/>
       <c r="R19" s="51" t="n">
         <v>27.1</v>
       </c>
@@ -1749,7 +1786,7 @@
       <c r="T19" s="51" t="n">
         <v>18.9</v>
       </c>
-      <c r="U19" s="51" t="inlineStr">
+      <c r="U19" s="63" t="inlineStr">
         <is>
           <t>ヤゲン904061／両端フランジ80mm／982061 V25ｲﾝｻｰﾄ＋台（図面実測）</t>
         </is>
@@ -1802,7 +1839,7 @@
       </c>
       <c r="L20" s="47" t="n"/>
       <c r="M20" s="47" t="n"/>
-      <c r="N20" s="48" t="n"/>
+      <c r="N20" s="61" t="n"/>
       <c r="O20" s="49">
         <f>IF(AND(G20="",H20=""),"",MAX(G20,H20))</f>
         <v/>
@@ -1811,7 +1848,7 @@
         <f>IF(OR(K20="",O20=""),"",K20-O20)</f>
         <v/>
       </c>
-      <c r="Q20" s="50" t="n"/>
+      <c r="Q20" s="62" t="n"/>
       <c r="R20" s="51" t="n">
         <v>27.8</v>
       </c>
@@ -1821,7 +1858,7 @@
       <c r="T20" s="51" t="n">
         <v>19.2</v>
       </c>
-      <c r="U20" s="51" t="inlineStr">
+      <c r="U20" s="63" t="inlineStr">
         <is>
           <t>ヤゲン904061／両端フランジ80mm／982061 V25ｲﾝｻｰﾄ＋台（図面実測）</t>
         </is>
@@ -1876,7 +1913,7 @@
       </c>
       <c r="L21" s="47" t="n"/>
       <c r="M21" s="47" t="n"/>
-      <c r="N21" s="48" t="n"/>
+      <c r="N21" s="61" t="n"/>
       <c r="O21" s="49">
         <f>IF(AND(G21="",H21=""),"",MAX(G21,H21))</f>
         <v/>
@@ -1885,7 +1922,7 @@
         <f>IF(OR(K21="",O21=""),"",K21-O21)</f>
         <v/>
       </c>
-      <c r="Q21" s="50" t="inlineStr">
+      <c r="Q21" s="62" t="inlineStr">
         <is>
           <t>印刷の 30／備考を修正液で消して 48 と記入。フランジB最小の欄に「ℓ200」</t>
         </is>
@@ -1899,7 +1936,7 @@
       <c r="T21" s="51" t="n">
         <v>18.5</v>
       </c>
-      <c r="U21" s="51" t="inlineStr">
+      <c r="U21" s="63" t="inlineStr">
         <is>
           <t>ヤゲン904061／両端フランジ80mm／982061 V25ｲﾝｻｰﾄ＋台（図面実測）</t>
         </is>
@@ -1954,7 +1991,7 @@
       </c>
       <c r="L22" s="47" t="n"/>
       <c r="M22" s="47" t="n"/>
-      <c r="N22" s="48" t="n"/>
+      <c r="N22" s="61" t="n"/>
       <c r="O22" s="49">
         <f>IF(AND(G22="",H22=""),"",MAX(G22,H22))</f>
         <v/>
@@ -1963,7 +2000,7 @@
         <f>IF(OR(K22="",O22=""),"",K22-O22)</f>
         <v/>
       </c>
-      <c r="Q22" s="50" t="inlineStr">
+      <c r="Q22" s="62" t="inlineStr">
         <is>
           <t>この行から4行を中かっこでまとめ「ℓ1500」と記入</t>
         </is>
@@ -1977,7 +2014,7 @@
       <c r="T22" s="51" t="n">
         <v>0.8</v>
       </c>
-      <c r="U22" s="51" t="inlineStr">
+      <c r="U22" s="63" t="inlineStr">
         <is>
           <t>ヤゲン904061／両端フランジ80mm／03500 V32</t>
         </is>
@@ -2032,7 +2069,7 @@
       </c>
       <c r="L23" s="47" t="n"/>
       <c r="M23" s="47" t="n"/>
-      <c r="N23" s="48" t="n"/>
+      <c r="N23" s="61" t="n"/>
       <c r="O23" s="49">
         <f>IF(AND(G23="",H23=""),"",MAX(G23,H23))</f>
         <v/>
@@ -2041,7 +2078,7 @@
         <f>IF(OR(K23="",O23=""),"",K23-O23)</f>
         <v/>
       </c>
-      <c r="Q23" s="50" t="n"/>
+      <c r="Q23" s="62" t="n"/>
       <c r="R23" s="51" t="n">
         <v>56.1</v>
       </c>
@@ -2051,7 +2088,7 @@
       <c r="T23" s="51" t="n">
         <v>0.9</v>
       </c>
-      <c r="U23" s="51" t="inlineStr">
+      <c r="U23" s="63" t="inlineStr">
         <is>
           <t>ヤゲン904061／両端フランジ80mm／03500 V32</t>
         </is>
@@ -2104,7 +2141,7 @@
       </c>
       <c r="L24" s="47" t="n"/>
       <c r="M24" s="47" t="n"/>
-      <c r="N24" s="48" t="n"/>
+      <c r="N24" s="61" t="n"/>
       <c r="O24" s="49">
         <f>IF(AND(G24="",H24=""),"",MAX(G24,H24))</f>
         <v/>
@@ -2113,7 +2150,7 @@
         <f>IF(OR(K24="",O24=""),"",K24-O24)</f>
         <v/>
       </c>
-      <c r="Q24" s="50" t="n"/>
+      <c r="Q24" s="62" t="n"/>
       <c r="R24" s="51" t="n">
         <v>56.7</v>
       </c>
@@ -2123,7 +2160,7 @@
       <c r="T24" s="51" t="n">
         <v>1.3</v>
       </c>
-      <c r="U24" s="51" t="inlineStr">
+      <c r="U24" s="63" t="inlineStr">
         <is>
           <t>ヤゲン904061／両端フランジ80mm／03500 V32</t>
         </is>
@@ -2178,7 +2215,7 @@
       </c>
       <c r="L25" s="47" t="n"/>
       <c r="M25" s="47" t="n"/>
-      <c r="N25" s="48" t="n"/>
+      <c r="N25" s="61" t="n"/>
       <c r="O25" s="49">
         <f>IF(AND(G25="",H25=""),"",MAX(G25,H25))</f>
         <v/>
@@ -2187,7 +2224,7 @@
         <f>IF(OR(K25="",O25=""),"",K25-O25)</f>
         <v/>
       </c>
-      <c r="Q25" s="53" t="inlineStr">
+      <c r="Q25" s="65" t="inlineStr">
         <is>
           <t>ℓ1500 のまとめはここまで</t>
         </is>
@@ -2201,7 +2238,7 @@
       <c r="T25" s="51" t="n">
         <v>1.7</v>
       </c>
-      <c r="U25" s="51" t="inlineStr">
+      <c r="U25" s="63" t="inlineStr">
         <is>
           <t>ヤゲン904061／両端フランジ80mm／03500 V32</t>
         </is>
@@ -2252,7 +2289,7 @@
       <c r="K26" s="47" t="n"/>
       <c r="L26" s="47" t="n"/>
       <c r="M26" s="47" t="n"/>
-      <c r="N26" s="48" t="n"/>
+      <c r="N26" s="61" t="n"/>
       <c r="O26" s="49">
         <f>IF(AND(G26="",H26=""),"",MAX(G26,H26))</f>
         <v/>
@@ -2261,7 +2298,7 @@
         <f>IF(OR(K26="",O26=""),"",K26-O26)</f>
         <v/>
       </c>
-      <c r="Q26" s="53" t="n"/>
+      <c r="Q26" s="65" t="n"/>
       <c r="R26" s="51" t="n">
         <v>54.4</v>
       </c>
@@ -2269,7 +2306,7 @@
         <v>54.4</v>
       </c>
       <c r="T26" s="51" t="n"/>
-      <c r="U26" s="51" t="inlineStr">
+      <c r="U26" s="63" t="inlineStr">
         <is>
           <t>ヤゲン904061／両端フランジ80mm／03600 V40</t>
         </is>
@@ -2309,7 +2346,7 @@
       <c r="K27" s="47" t="n"/>
       <c r="L27" s="47" t="n"/>
       <c r="M27" s="47" t="n"/>
-      <c r="N27" s="48" t="n"/>
+      <c r="N27" s="61" t="n"/>
       <c r="O27" s="49">
         <f>IF(AND(G27="",H27=""),"",MAX(G27,H27))</f>
         <v/>
@@ -2318,7 +2355,7 @@
         <f>IF(OR(K27="",O27=""),"",K27-O27)</f>
         <v/>
       </c>
-      <c r="Q27" s="53" t="n"/>
+      <c r="Q27" s="65" t="n"/>
       <c r="R27" s="51" t="n">
         <v>56.1</v>
       </c>
@@ -2326,7 +2363,7 @@
         <v>56.1</v>
       </c>
       <c r="T27" s="51" t="n"/>
-      <c r="U27" s="51" t="inlineStr">
+      <c r="U27" s="63" t="inlineStr">
         <is>
           <t>ヤゲン904061／両端フランジ80mm／03600 V40</t>
         </is>
@@ -2364,7 +2401,7 @@
       <c r="K28" s="47" t="n"/>
       <c r="L28" s="47" t="n"/>
       <c r="M28" s="47" t="n"/>
-      <c r="N28" s="48" t="n"/>
+      <c r="N28" s="61" t="n"/>
       <c r="O28" s="49">
         <f>IF(AND(G28="",H28=""),"",MAX(G28,H28))</f>
         <v/>
@@ -2373,7 +2410,7 @@
         <f>IF(OR(K28="",O28=""),"",K28-O28)</f>
         <v/>
       </c>
-      <c r="Q28" s="53" t="n"/>
+      <c r="Q28" s="65" t="n"/>
       <c r="R28" s="51" t="n">
         <v>56.6</v>
       </c>
@@ -2381,7 +2418,7 @@
         <v>56.6</v>
       </c>
       <c r="T28" s="51" t="n"/>
-      <c r="U28" s="51" t="inlineStr">
+      <c r="U28" s="63" t="inlineStr">
         <is>
           <t>ヤゲン904061／両端フランジ80mm／03600 V40</t>
         </is>
@@ -2421,7 +2458,7 @@
       <c r="K29" s="47" t="n"/>
       <c r="L29" s="47" t="n"/>
       <c r="M29" s="47" t="n"/>
-      <c r="N29" s="48" t="n"/>
+      <c r="N29" s="61" t="n"/>
       <c r="O29" s="49">
         <f>IF(AND(G29="",H29=""),"",MAX(G29,H29))</f>
         <v/>
@@ -2430,7 +2467,7 @@
         <f>IF(OR(K29="",O29=""),"",K29-O29)</f>
         <v/>
       </c>
-      <c r="Q29" s="53" t="n"/>
+      <c r="Q29" s="65" t="n"/>
       <c r="R29" s="51" t="n">
         <v>58.1</v>
       </c>
@@ -2438,7 +2475,7 @@
         <v>58.1</v>
       </c>
       <c r="T29" s="51" t="n"/>
-      <c r="U29" s="51" t="inlineStr">
+      <c r="U29" s="63" t="inlineStr">
         <is>
           <t>ヤゲン904061／両端フランジ80mm／03600 V40</t>
         </is>
@@ -2478,7 +2515,7 @@
       <c r="K30" s="47" t="n"/>
       <c r="L30" s="47" t="n"/>
       <c r="M30" s="47" t="n"/>
-      <c r="N30" s="48" t="n"/>
+      <c r="N30" s="61" t="n"/>
       <c r="O30" s="49">
         <f>IF(AND(G30="",H30=""),"",MAX(G30,H30))</f>
         <v/>
@@ -2487,7 +2524,7 @@
         <f>IF(OR(K30="",O30=""),"",K30-O30)</f>
         <v/>
       </c>
-      <c r="Q30" s="53" t="n"/>
+      <c r="Q30" s="65" t="n"/>
       <c r="R30" s="51" t="n">
         <v>63.1</v>
       </c>
@@ -2495,7 +2532,7 @@
         <v>63.1</v>
       </c>
       <c r="T30" s="51" t="n"/>
-      <c r="U30" s="51" t="inlineStr">
+      <c r="U30" s="63" t="inlineStr">
         <is>
           <t>ヤゲン904061／両端フランジ80mm／03600 V40</t>
         </is>
@@ -2533,7 +2570,7 @@
       <c r="K31" s="47" t="n"/>
       <c r="L31" s="47" t="n"/>
       <c r="M31" s="47" t="n"/>
-      <c r="N31" s="48" t="n"/>
+      <c r="N31" s="61" t="n"/>
       <c r="O31" s="49">
         <f>IF(AND(G31="",H31=""),"",MAX(G31,H31))</f>
         <v/>
@@ -2542,7 +2579,7 @@
         <f>IF(OR(K31="",O31=""),"",K31-O31)</f>
         <v/>
       </c>
-      <c r="Q31" s="53" t="n"/>
+      <c r="Q31" s="65" t="n"/>
       <c r="R31" s="51" t="n">
         <v>45</v>
       </c>
@@ -2550,7 +2587,7 @@
         <v>45</v>
       </c>
       <c r="T31" s="51" t="n"/>
-      <c r="U31" s="51" t="inlineStr">
+      <c r="U31" s="63" t="inlineStr">
         <is>
           <t>ヤゲン904061／両端フランジ80mm／03700 V50</t>
         </is>
@@ -2588,7 +2625,7 @@
       <c r="K32" s="47" t="n"/>
       <c r="L32" s="47" t="n"/>
       <c r="M32" s="47" t="n"/>
-      <c r="N32" s="48" t="n"/>
+      <c r="N32" s="61" t="n"/>
       <c r="O32" s="49">
         <f>IF(AND(G32="",H32=""),"",MAX(G32,H32))</f>
         <v/>
@@ -2597,7 +2634,7 @@
         <f>IF(OR(K32="",O32=""),"",K32-O32)</f>
         <v/>
       </c>
-      <c r="Q32" s="53" t="n"/>
+      <c r="Q32" s="65" t="n"/>
       <c r="R32" s="51" t="n">
         <v>47</v>
       </c>
@@ -2605,7 +2642,7 @@
         <v>47</v>
       </c>
       <c r="T32" s="51" t="n"/>
-      <c r="U32" s="51" t="inlineStr">
+      <c r="U32" s="63" t="inlineStr">
         <is>
           <t>ヤゲン904061／両端フランジ80mm／03700 V50</t>
         </is>
@@ -2645,7 +2682,7 @@
       <c r="K33" s="47" t="n"/>
       <c r="L33" s="47" t="n"/>
       <c r="M33" s="47" t="n"/>
-      <c r="N33" s="48" t="n"/>
+      <c r="N33" s="61" t="n"/>
       <c r="O33" s="49">
         <f>IF(AND(G33="",H33=""),"",MAX(G33,H33))</f>
         <v/>
@@ -2654,7 +2691,7 @@
         <f>IF(OR(K33="",O33=""),"",K33-O33)</f>
         <v/>
       </c>
-      <c r="Q33" s="53" t="n"/>
+      <c r="Q33" s="65" t="n"/>
       <c r="R33" s="51" t="n">
         <v>59.7</v>
       </c>
@@ -2662,7 +2699,7 @@
         <v>59.7</v>
       </c>
       <c r="T33" s="51" t="n"/>
-      <c r="U33" s="51" t="inlineStr">
+      <c r="U33" s="63" t="inlineStr">
         <is>
           <t>ヤゲン904061／両端フランジ80mm／03800 V63</t>
         </is>
@@ -2700,7 +2737,7 @@
       <c r="K34" s="47" t="n"/>
       <c r="L34" s="47" t="n"/>
       <c r="M34" s="47" t="n"/>
-      <c r="N34" s="48" t="n"/>
+      <c r="N34" s="61" t="n"/>
       <c r="O34" s="49">
         <f>IF(AND(G34="",H34=""),"",MAX(G34,H34))</f>
         <v/>
@@ -2709,7 +2746,7 @@
         <f>IF(OR(K34="",O34=""),"",K34-O34)</f>
         <v/>
       </c>
-      <c r="Q34" s="53" t="n"/>
+      <c r="Q34" s="65" t="n"/>
       <c r="R34" s="51" t="n">
         <v>71</v>
       </c>
@@ -2717,7 +2754,7 @@
         <v>71</v>
       </c>
       <c r="T34" s="51" t="n"/>
-      <c r="U34" s="51" t="inlineStr">
+      <c r="U34" s="63" t="inlineStr">
         <is>
           <t>ヤゲン904061／両端フランジ80mm／01360 V80</t>
         </is>
@@ -2755,7 +2792,7 @@
       <c r="K35" s="47" t="n"/>
       <c r="L35" s="47" t="n"/>
       <c r="M35" s="47" t="n"/>
-      <c r="N35" s="48" t="n"/>
+      <c r="N35" s="61" t="n"/>
       <c r="O35" s="49">
         <f>IF(AND(G35="",H35=""),"",MAX(G35,H35))</f>
         <v/>
@@ -2764,7 +2801,7 @@
         <f>IF(OR(K35="",O35=""),"",K35-O35)</f>
         <v/>
       </c>
-      <c r="Q35" s="53" t="n"/>
+      <c r="Q35" s="65" t="n"/>
       <c r="R35" s="51" t="n">
         <v>72</v>
       </c>
@@ -2772,7 +2809,7 @@
         <v>72</v>
       </c>
       <c r="T35" s="51" t="n"/>
-      <c r="U35" s="51" t="inlineStr">
+      <c r="U35" s="63" t="inlineStr">
         <is>
           <t>ヤゲン904061／両端フランジ80mm／01360 V80</t>
         </is>
@@ -2810,7 +2847,7 @@
       <c r="K36" s="47" t="n"/>
       <c r="L36" s="47" t="n"/>
       <c r="M36" s="47" t="n"/>
-      <c r="N36" s="48" t="n"/>
+      <c r="N36" s="61" t="n"/>
       <c r="O36" s="49">
         <f>IF(AND(G36="",H36=""),"",MAX(G36,H36))</f>
         <v/>
@@ -2819,7 +2856,7 @@
         <f>IF(OR(K36="",O36=""),"",K36-O36)</f>
         <v/>
       </c>
-      <c r="Q36" s="53" t="n"/>
+      <c r="Q36" s="65" t="n"/>
       <c r="R36" s="51" t="n">
         <v>73.90000000000001</v>
       </c>
@@ -2827,7 +2864,7 @@
         <v>73.90000000000001</v>
       </c>
       <c r="T36" s="51" t="n"/>
-      <c r="U36" s="51" t="inlineStr">
+      <c r="U36" s="63" t="inlineStr">
         <is>
           <t>ヤゲン904061／両端フランジ80mm／01360 V80</t>
         </is>
@@ -2865,7 +2902,7 @@
       <c r="K37" s="47" t="n"/>
       <c r="L37" s="47" t="n"/>
       <c r="M37" s="47" t="n"/>
-      <c r="N37" s="48" t="n"/>
+      <c r="N37" s="61" t="n"/>
       <c r="O37" s="49">
         <f>IF(AND(G37="",H37=""),"",MAX(G37,H37))</f>
         <v/>
@@ -2874,7 +2911,7 @@
         <f>IF(OR(K37="",O37=""),"",K37-O37)</f>
         <v/>
       </c>
-      <c r="Q37" s="53" t="n"/>
+      <c r="Q37" s="65" t="n"/>
       <c r="R37" s="51" t="inlineStr">
         <is>
           <t>算出できず</t>
@@ -2882,7 +2919,7 @@
       </c>
       <c r="S37" s="51" t="n"/>
       <c r="T37" s="51" t="n"/>
-      <c r="U37" s="51" t="inlineStr">
+      <c r="U37" s="63" t="inlineStr">
         <is>
           <t>段差を広げても不可</t>
         </is>
@@ -2920,7 +2957,7 @@
       <c r="K38" s="47" t="n"/>
       <c r="L38" s="47" t="n"/>
       <c r="M38" s="47" t="n"/>
-      <c r="N38" s="48" t="n"/>
+      <c r="N38" s="61" t="n"/>
       <c r="O38" s="49">
         <f>IF(AND(G38="",H38=""),"",MAX(G38,H38))</f>
         <v/>
@@ -2929,7 +2966,7 @@
         <f>IF(OR(K38="",O38=""),"",K38-O38)</f>
         <v/>
       </c>
-      <c r="Q38" s="53" t="n"/>
+      <c r="Q38" s="65" t="n"/>
       <c r="R38" s="51" t="inlineStr">
         <is>
           <t>算出できず</t>
@@ -2937,7 +2974,7 @@
       </c>
       <c r="S38" s="51" t="n"/>
       <c r="T38" s="51" t="n"/>
-      <c r="U38" s="51" t="inlineStr">
+      <c r="U38" s="63" t="inlineStr">
         <is>
           <t>段差を広げても不可</t>
         </is>
@@ -2975,7 +3012,7 @@
       <c r="K39" s="47" t="n"/>
       <c r="L39" s="47" t="n"/>
       <c r="M39" s="47" t="n"/>
-      <c r="N39" s="48" t="n"/>
+      <c r="N39" s="61" t="n"/>
       <c r="O39" s="49">
         <f>IF(AND(G39="",H39=""),"",MAX(G39,H39))</f>
         <v/>
@@ -2984,7 +3021,7 @@
         <f>IF(OR(K39="",O39=""),"",K39-O39)</f>
         <v/>
       </c>
-      <c r="Q39" s="53" t="n"/>
+      <c r="Q39" s="65" t="n"/>
       <c r="R39" s="51" t="inlineStr">
         <is>
           <t>算出できず</t>
@@ -2992,7 +3029,7 @@
       </c>
       <c r="S39" s="51" t="n"/>
       <c r="T39" s="51" t="n"/>
-      <c r="U39" s="51" t="inlineStr">
+      <c r="U39" s="63" t="inlineStr">
         <is>
           <t>段差を広げても不可</t>
         </is>
@@ -3030,7 +3067,7 @@
       <c r="K40" s="47" t="n"/>
       <c r="L40" s="47" t="n"/>
       <c r="M40" s="47" t="n"/>
-      <c r="N40" s="48" t="n"/>
+      <c r="N40" s="61" t="n"/>
       <c r="O40" s="49">
         <f>IF(AND(G40="",H40=""),"",MAX(G40,H40))</f>
         <v/>
@@ -3039,7 +3076,7 @@
         <f>IF(OR(K40="",O40=""),"",K40-O40)</f>
         <v/>
       </c>
-      <c r="Q40" s="53" t="n"/>
+      <c r="Q40" s="65" t="n"/>
       <c r="R40" s="51" t="inlineStr">
         <is>
           <t>算出できず</t>
@@ -3047,7 +3084,7 @@
       </c>
       <c r="S40" s="51" t="n"/>
       <c r="T40" s="51" t="n"/>
-      <c r="U40" s="51" t="inlineStr">
+      <c r="U40" s="63" t="inlineStr">
         <is>
           <t>段差を広げても不可</t>
         </is>
@@ -3085,7 +3122,7 @@
       <c r="K41" s="47" t="n"/>
       <c r="L41" s="47" t="n"/>
       <c r="M41" s="47" t="n"/>
-      <c r="N41" s="48" t="n"/>
+      <c r="N41" s="61" t="n"/>
       <c r="O41" s="49">
         <f>IF(AND(G41="",H41=""),"",MAX(G41,H41))</f>
         <v/>
@@ -3094,7 +3131,7 @@
         <f>IF(OR(K41="",O41=""),"",K41-O41)</f>
         <v/>
       </c>
-      <c r="Q41" s="53" t="n"/>
+      <c r="Q41" s="65" t="n"/>
       <c r="R41" s="51" t="inlineStr">
         <is>
           <t>算出できず</t>
@@ -3102,7 +3139,7 @@
       </c>
       <c r="S41" s="51" t="n"/>
       <c r="T41" s="51" t="n"/>
-      <c r="U41" s="51" t="inlineStr">
+      <c r="U41" s="63" t="inlineStr">
         <is>
           <t>段差を広げても不可</t>
         </is>
@@ -3140,7 +3177,7 @@
       <c r="K42" s="47" t="n"/>
       <c r="L42" s="47" t="n"/>
       <c r="M42" s="47" t="n"/>
-      <c r="N42" s="48" t="n"/>
+      <c r="N42" s="61" t="n"/>
       <c r="O42" s="49">
         <f>IF(AND(G42="",H42=""),"",MAX(G42,H42))</f>
         <v/>
@@ -3149,7 +3186,7 @@
         <f>IF(OR(K42="",O42=""),"",K42-O42)</f>
         <v/>
       </c>
-      <c r="Q42" s="53" t="n"/>
+      <c r="Q42" s="65" t="n"/>
       <c r="R42" s="51" t="inlineStr">
         <is>
           <t>算出できず</t>
@@ -3157,7 +3194,7 @@
       </c>
       <c r="S42" s="51" t="n"/>
       <c r="T42" s="51" t="n"/>
-      <c r="U42" s="51" t="inlineStr">
+      <c r="U42" s="63" t="inlineStr">
         <is>
           <t>段差を広げても不可</t>
         </is>
@@ -3181,10 +3218,11 @@
       <c r="K43" s="33" t="n"/>
       <c r="L43" s="33" t="n"/>
       <c r="M43" s="33" t="n"/>
-      <c r="N43" s="33" t="n"/>
+      <c r="N43" s="59" t="n"/>
       <c r="O43" s="33" t="n"/>
       <c r="P43" s="33" t="n"/>
-      <c r="Q43" s="33" t="n"/>
+      <c r="Q43" s="59" t="n"/>
+      <c r="U43" s="60" t="n"/>
     </row>
     <row r="44" ht="15" customHeight="1" s="28">
       <c r="A44" s="44" t="inlineStr">
@@ -3218,7 +3256,7 @@
       <c r="K44" s="47" t="n"/>
       <c r="L44" s="47" t="n"/>
       <c r="M44" s="47" t="n"/>
-      <c r="N44" s="48" t="n"/>
+      <c r="N44" s="61" t="n"/>
       <c r="O44" s="49">
         <f>IF(AND(G44="",H44=""),"",MAX(G44,H44))</f>
         <v/>
@@ -3227,7 +3265,7 @@
         <f>IF(OR(K44="",O44=""),"",K44-O44)</f>
         <v/>
       </c>
-      <c r="Q44" s="53" t="n"/>
+      <c r="Q44" s="65" t="n"/>
       <c r="R44" s="51" t="n">
         <v>23.2</v>
       </c>
@@ -3235,7 +3273,7 @@
         <v>23.2</v>
       </c>
       <c r="T44" s="51" t="n"/>
-      <c r="U44" s="51" t="inlineStr">
+      <c r="U44" s="63" t="inlineStr">
         <is>
           <t>ヤゲン904061／両端フランジ80mm／982061 V25ｲﾝｻｰﾄ＋台（図面実測）</t>
         </is>
@@ -3273,7 +3311,7 @@
       <c r="K45" s="47" t="n"/>
       <c r="L45" s="47" t="n"/>
       <c r="M45" s="47" t="n"/>
-      <c r="N45" s="48" t="n"/>
+      <c r="N45" s="61" t="n"/>
       <c r="O45" s="49">
         <f>IF(AND(G45="",H45=""),"",MAX(G45,H45))</f>
         <v/>
@@ -3282,7 +3320,7 @@
         <f>IF(OR(K45="",O45=""),"",K45-O45)</f>
         <v/>
       </c>
-      <c r="Q45" s="53" t="n"/>
+      <c r="Q45" s="65" t="n"/>
       <c r="R45" s="51" t="n">
         <v>24.7</v>
       </c>
@@ -3290,7 +3328,7 @@
         <v>24.7</v>
       </c>
       <c r="T45" s="51" t="n"/>
-      <c r="U45" s="51" t="inlineStr">
+      <c r="U45" s="63" t="inlineStr">
         <is>
           <t>ヤゲン904061／両端フランジ80mm／982061 V25ｲﾝｻｰﾄ＋台（図面実測）</t>
         </is>
@@ -3328,7 +3366,7 @@
       <c r="K46" s="47" t="n"/>
       <c r="L46" s="47" t="n"/>
       <c r="M46" s="47" t="n"/>
-      <c r="N46" s="48" t="n"/>
+      <c r="N46" s="61" t="n"/>
       <c r="O46" s="49">
         <f>IF(AND(G46="",H46=""),"",MAX(G46,H46))</f>
         <v/>
@@ -3337,7 +3375,7 @@
         <f>IF(OR(K46="",O46=""),"",K46-O46)</f>
         <v/>
       </c>
-      <c r="Q46" s="53" t="n"/>
+      <c r="Q46" s="65" t="n"/>
       <c r="R46" s="51" t="n">
         <v>27.1</v>
       </c>
@@ -3345,7 +3383,7 @@
         <v>27.1</v>
       </c>
       <c r="T46" s="51" t="n"/>
-      <c r="U46" s="51" t="inlineStr">
+      <c r="U46" s="63" t="inlineStr">
         <is>
           <t>ヤゲン904061／両端フランジ80mm／982061 V25ｲﾝｻｰﾄ＋台（図面実測）</t>
         </is>
@@ -3383,7 +3421,7 @@
       <c r="K47" s="47" t="n"/>
       <c r="L47" s="47" t="n"/>
       <c r="M47" s="47" t="n"/>
-      <c r="N47" s="48" t="n"/>
+      <c r="N47" s="61" t="n"/>
       <c r="O47" s="49">
         <f>IF(AND(G47="",H47=""),"",MAX(G47,H47))</f>
         <v/>
@@ -3392,7 +3430,7 @@
         <f>IF(OR(K47="",O47=""),"",K47-O47)</f>
         <v/>
       </c>
-      <c r="Q47" s="53" t="n"/>
+      <c r="Q47" s="65" t="n"/>
       <c r="R47" s="51" t="n">
         <v>53.5</v>
       </c>
@@ -3400,7 +3438,7 @@
         <v>53.5</v>
       </c>
       <c r="T47" s="51" t="n"/>
-      <c r="U47" s="51" t="inlineStr">
+      <c r="U47" s="63" t="inlineStr">
         <is>
           <t>ヤゲン904061／両端フランジ80mm／03600 V40</t>
         </is>
@@ -3438,7 +3476,7 @@
       <c r="K48" s="47" t="n"/>
       <c r="L48" s="47" t="n"/>
       <c r="M48" s="47" t="n"/>
-      <c r="N48" s="48" t="n"/>
+      <c r="N48" s="61" t="n"/>
       <c r="O48" s="49">
         <f>IF(AND(G48="",H48=""),"",MAX(G48,H48))</f>
         <v/>
@@ -3447,7 +3485,7 @@
         <f>IF(OR(K48="",O48=""),"",K48-O48)</f>
         <v/>
       </c>
-      <c r="Q48" s="53" t="n"/>
+      <c r="Q48" s="65" t="n"/>
       <c r="R48" s="51" t="n">
         <v>56.1</v>
       </c>
@@ -3455,7 +3493,7 @@
         <v>56.1</v>
       </c>
       <c r="T48" s="51" t="n"/>
-      <c r="U48" s="51" t="inlineStr">
+      <c r="U48" s="63" t="inlineStr">
         <is>
           <t>ヤゲン904061／両端フランジ80mm／03600 V40</t>
         </is>
@@ -3493,7 +3531,7 @@
       <c r="K49" s="47" t="n"/>
       <c r="L49" s="47" t="n"/>
       <c r="M49" s="47" t="n"/>
-      <c r="N49" s="48" t="n"/>
+      <c r="N49" s="61" t="n"/>
       <c r="O49" s="49">
         <f>IF(AND(G49="",H49=""),"",MAX(G49,H49))</f>
         <v/>
@@ -3502,7 +3540,7 @@
         <f>IF(OR(K49="",O49=""),"",K49-O49)</f>
         <v/>
       </c>
-      <c r="Q49" s="53" t="n"/>
+      <c r="Q49" s="65" t="n"/>
       <c r="R49" s="51" t="n">
         <v>58.1</v>
       </c>
@@ -3510,7 +3548,7 @@
         <v>58.1</v>
       </c>
       <c r="T49" s="51" t="n"/>
-      <c r="U49" s="51" t="inlineStr">
+      <c r="U49" s="63" t="inlineStr">
         <is>
           <t>ヤゲン904061／両端フランジ80mm／03600 V40</t>
         </is>
@@ -3548,7 +3586,7 @@
       <c r="K50" s="47" t="n"/>
       <c r="L50" s="47" t="n"/>
       <c r="M50" s="47" t="n"/>
-      <c r="N50" s="48" t="n"/>
+      <c r="N50" s="61" t="n"/>
       <c r="O50" s="49">
         <f>IF(AND(G50="",H50=""),"",MAX(G50,H50))</f>
         <v/>
@@ -3557,7 +3595,7 @@
         <f>IF(OR(K50="",O50=""),"",K50-O50)</f>
         <v/>
       </c>
-      <c r="Q50" s="53" t="n"/>
+      <c r="Q50" s="65" t="n"/>
       <c r="R50" s="51" t="n">
         <v>71</v>
       </c>
@@ -3565,7 +3603,7 @@
         <v>71</v>
       </c>
       <c r="T50" s="51" t="n"/>
-      <c r="U50" s="51" t="inlineStr">
+      <c r="U50" s="63" t="inlineStr">
         <is>
           <t>ヤゲン904061／両端フランジ80mm／01360 V80</t>
         </is>
@@ -3603,7 +3641,7 @@
       <c r="K51" s="47" t="n"/>
       <c r="L51" s="47" t="n"/>
       <c r="M51" s="47" t="n"/>
-      <c r="N51" s="48" t="n"/>
+      <c r="N51" s="61" t="n"/>
       <c r="O51" s="49">
         <f>IF(AND(G51="",H51=""),"",MAX(G51,H51))</f>
         <v/>
@@ -3612,7 +3650,7 @@
         <f>IF(OR(K51="",O51=""),"",K51-O51)</f>
         <v/>
       </c>
-      <c r="Q51" s="53" t="n"/>
+      <c r="Q51" s="65" t="n"/>
       <c r="R51" s="51" t="n">
         <v>73.90000000000001</v>
       </c>
@@ -3620,7 +3658,7 @@
         <v>73.90000000000001</v>
       </c>
       <c r="T51" s="51" t="n"/>
-      <c r="U51" s="51" t="inlineStr">
+      <c r="U51" s="63" t="inlineStr">
         <is>
           <t>ヤゲン904061／両端フランジ80mm／01360 V80</t>
         </is>
@@ -3933,63 +3971,63 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
+      <c r="A76" s="27" t="inlineStr">
         <is>
           <t>※【重要な訂正】I列は「フランジA 最小」という見出しでしたが、実際には</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
+      <c r="A77" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">　 その行の段差Sのときに取れる フランジAの“最大” です（超えるとVの台に当たる）。</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
+      <c r="A78" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">　 例：V8・PL1.2・S=15.5 のとき A は 49 まで。50 にすると曲がりません。</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
+      <c r="A79" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">　 備考欄の「S35の場合 A95」は、段差を35にすればAを95まで伸ばせるという意味です。</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
+      <c r="A80" s="27" t="inlineStr">
         <is>
           <t>※ V〜X列は、同じ段差Sでシミュレーションが出したフランジAの上限です。</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
+      <c r="A81" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">　 条件：上型ヤゲン904061、反対側のフランジBは30mm固定（A側だけを見るため）。</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
+      <c r="A82" s="27" t="inlineStr">
         <is>
           <t>※ 突き合わせの結果：V25・V32 は実績とほぼ一致（差0.5〜4.5mm）。V8 はシミュレーションが</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
+      <c r="A83" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">　 3.4〜3.7mm 厳しめ。いっぽう V12・V16・V20 はシミュレーションが 40〜48mm も甘く出ます。</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
+      <c r="A84" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">　 実績では50mm前後で台に当たるのに、モデルには その高さの障害物がありません。要調査。</t>
         </is>
@@ -4015,8 +4053,8 @@
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <printOptions horizontalCentered="1" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <pageMargins left="0.25" right="0.25" top="0.35" bottom="0.35" header="0.2" footer="0.2"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>